--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,250 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114786104</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56449</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stora Uvberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>574091</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6569646</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114785700</v>
+      </c>
+      <c r="B16" t="n">
+        <v>89660</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stora Uvberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>574091</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6569646</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i sydläge</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -2183,11 +2183,11 @@
         <v>114786104</v>
       </c>
       <c r="B15" t="n">
-        <v>56478</v>
+        <v>56582</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>114786104</v>
       </c>
       <c r="B15" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>114786104</v>
       </c>
       <c r="B15" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -2198,11 +2198,6 @@
       <c r="E15" t="n">
         <v>100138</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>114786104</v>
       </c>
       <c r="B15" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,6 +2197,11 @@
       </c>
       <c r="E15" t="n">
         <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/artfynd/A 52556-2019 artfynd.xlsx
+++ b/artfynd/A 52556-2019 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>114786104</v>
       </c>
       <c r="B15" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
